--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/144.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/144.xlsx
@@ -426,13 +426,13 @@
         <v>-7.201132586970965</v>
       </c>
       <c r="E2">
-        <v>-13.07037810845629</v>
+        <v>-17.01442990306674</v>
       </c>
       <c r="F2">
-        <v>-0.8713921245810169</v>
+        <v>-0.8219808373714291</v>
       </c>
       <c r="G2">
-        <v>-5.958638824620387</v>
+        <v>-8.818384067263477</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.174328926993075</v>
       </c>
       <c r="E3">
-        <v>-12.73719110486793</v>
+        <v>-16.1779437697919</v>
       </c>
       <c r="F3">
-        <v>-1.157003264657453</v>
+        <v>-0.641168942525367</v>
       </c>
       <c r="G3">
-        <v>-6.541771558089771</v>
+        <v>-7.740629345862663</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.229785453967386</v>
       </c>
       <c r="E4">
-        <v>-14.2774337982528</v>
+        <v>-17.12738363024007</v>
       </c>
       <c r="F4">
-        <v>-1.340867693382831</v>
+        <v>-0.8716572021499127</v>
       </c>
       <c r="G4">
-        <v>-5.820771155637438</v>
+        <v>-7.298588752731478</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.26156213434092</v>
       </c>
       <c r="E5">
-        <v>-14.80270961229852</v>
+        <v>-17.53609652332835</v>
       </c>
       <c r="F5">
-        <v>-1.580140789314066</v>
+        <v>-0.652056175300361</v>
       </c>
       <c r="G5">
-        <v>-5.750044660736449</v>
+        <v>-7.292232505296077</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.25362243881578</v>
       </c>
       <c r="E6">
-        <v>-15.9842971642759</v>
+        <v>-17.46955965473365</v>
       </c>
       <c r="F6">
-        <v>-1.291516876993648</v>
+        <v>-0.8175209072747567</v>
       </c>
       <c r="G6">
-        <v>-5.304465094423782</v>
+        <v>-7.879106155224838</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.15119062943087</v>
       </c>
       <c r="E7">
-        <v>-13.88956094254782</v>
+        <v>-18.31090936909273</v>
       </c>
       <c r="F7">
-        <v>-0.8658196970623846</v>
+        <v>-0.9027508009813949</v>
       </c>
       <c r="G7">
-        <v>-4.320766282339203</v>
+        <v>-6.915456006926084</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.92377936454323</v>
       </c>
       <c r="E8">
-        <v>-16.46291611062059</v>
+        <v>-19.28465354954006</v>
       </c>
       <c r="F8">
-        <v>-0.7977635163505856</v>
+        <v>-1.000571879210586</v>
       </c>
       <c r="G8">
-        <v>-3.554378300543461</v>
+        <v>-6.477894581909533</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.52935324594953</v>
       </c>
       <c r="E9">
-        <v>-17.05941123538494</v>
+        <v>-18.5014086851734</v>
       </c>
       <c r="F9">
-        <v>-1.466081224887796</v>
+        <v>-0.9841967123920452</v>
       </c>
       <c r="G9">
-        <v>-2.259756361956071</v>
+        <v>-6.00186792827219</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.93740523408582</v>
       </c>
       <c r="E10">
-        <v>-15.13696986422669</v>
+        <v>-19.23961787553378</v>
       </c>
       <c r="F10">
-        <v>-1.516828668718099</v>
+        <v>-1.147511830956176</v>
       </c>
       <c r="G10">
-        <v>-2.917313469693811</v>
+        <v>-5.399603552131357</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.11914835118704</v>
       </c>
       <c r="E11">
-        <v>-16.41149528826349</v>
+        <v>-21.28887010432882</v>
       </c>
       <c r="F11">
-        <v>-1.861576129312989</v>
+        <v>-0.9796315796352171</v>
       </c>
       <c r="G11">
-        <v>-3.107342094193516</v>
+        <v>-4.502452332079944</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.0645021303225</v>
       </c>
       <c r="E12">
-        <v>-19.34468752945975</v>
+        <v>-21.20087732588578</v>
       </c>
       <c r="F12">
-        <v>-1.14164533300955</v>
+        <v>-1.220597030170371</v>
       </c>
       <c r="G12">
-        <v>-1.775185190281869</v>
+        <v>-4.388990004812503</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.76774817059279</v>
       </c>
       <c r="E13">
-        <v>-17.87203683911337</v>
+        <v>-21.46838787094089</v>
       </c>
       <c r="F13">
-        <v>-1.418094729611023</v>
+        <v>-1.06627135466142</v>
       </c>
       <c r="G13">
-        <v>-1.858971787335284</v>
+        <v>-3.511327966350779</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.24289934435473</v>
       </c>
       <c r="E14">
-        <v>-21.0318022203354</v>
+        <v>-22.94018267969982</v>
       </c>
       <c r="F14">
-        <v>-1.657062986338028</v>
+        <v>-1.50811755711026</v>
       </c>
       <c r="G14">
-        <v>-2.171467422969248</v>
+        <v>-3.216232558071224</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.51063612084328</v>
       </c>
       <c r="E15">
-        <v>-19.03743962498733</v>
+        <v>-23.25515616082933</v>
       </c>
       <c r="F15">
-        <v>-1.818496882530401</v>
+        <v>-1.198344596628968</v>
       </c>
       <c r="G15">
-        <v>-1.18466994025991</v>
+        <v>-3.072435702027441</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.60081575845146</v>
       </c>
       <c r="E16">
-        <v>-21.47981321086224</v>
+        <v>-23.88879382940459</v>
       </c>
       <c r="F16">
-        <v>-1.397832034571145</v>
+        <v>-1.313355126833651</v>
       </c>
       <c r="G16">
-        <v>-1.69273605362632</v>
+        <v>-2.677398234462828</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.54996387350497</v>
       </c>
       <c r="E17">
-        <v>-21.46874562038749</v>
+        <v>-25.07999533170025</v>
       </c>
       <c r="F17">
-        <v>-1.089312393970288</v>
+        <v>-0.9979500963807254</v>
       </c>
       <c r="G17">
-        <v>-0.02759454773815926</v>
+        <v>-2.538153378535542</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.399686304049657</v>
       </c>
       <c r="E18">
-        <v>-22.35713712273825</v>
+        <v>-25.32102336075851</v>
       </c>
       <c r="F18">
-        <v>-1.674587927111654</v>
+        <v>-1.166067260778885</v>
       </c>
       <c r="G18">
-        <v>1.036464446766689</v>
+        <v>-1.951544572249924</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.189301110801946</v>
       </c>
       <c r="E19">
-        <v>-24.08432428010778</v>
+        <v>-25.74046420877096</v>
       </c>
       <c r="F19">
-        <v>-1.634923210763405</v>
+        <v>-0.9560347057990704</v>
       </c>
       <c r="G19">
-        <v>0.3892594149302508</v>
+        <v>-1.39648195440802</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.968370925694405</v>
       </c>
       <c r="E20">
-        <v>-26.24778009490225</v>
+        <v>-26.3333546682252</v>
       </c>
       <c r="F20">
-        <v>-0.6922328227035398</v>
+        <v>-0.876894969237814</v>
       </c>
       <c r="G20">
-        <v>1.081057495180672</v>
+        <v>-1.301995674171681</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.777054641266565</v>
       </c>
       <c r="E21">
-        <v>-24.02407293343572</v>
+        <v>-26.9223279976628</v>
       </c>
       <c r="F21">
-        <v>-1.36778217866719</v>
+        <v>-0.7492037908310758</v>
       </c>
       <c r="G21">
-        <v>1.749800936295609</v>
+        <v>-1.153868624562531</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.650459935993389</v>
       </c>
       <c r="E22">
-        <v>-24.88657967835864</v>
+        <v>-28.04532162445494</v>
       </c>
       <c r="F22">
-        <v>-1.049718088851278</v>
+        <v>-0.6979841775811768</v>
       </c>
       <c r="G22">
-        <v>2.508621010988576</v>
+        <v>-1.630074047658995</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.618075710447022</v>
       </c>
       <c r="E23">
-        <v>-25.18149654810817</v>
+        <v>-28.44786220747076</v>
       </c>
       <c r="F23">
-        <v>-0.7458455893801266</v>
+        <v>-0.5520581475366131</v>
       </c>
       <c r="G23">
-        <v>1.140432129427501</v>
+        <v>-0.9005754748073534</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.70250425224668</v>
       </c>
       <c r="E24">
-        <v>-26.85024374840871</v>
+        <v>-28.89278930719838</v>
       </c>
       <c r="F24">
-        <v>-0.5188107934578521</v>
+        <v>-0.6793144330568816</v>
       </c>
       <c r="G24">
-        <v>1.566780736702541</v>
+        <v>-0.8989864129485033</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.917837785124837</v>
       </c>
       <c r="E25">
-        <v>-26.20580566932516</v>
+        <v>-28.81869894395889</v>
       </c>
       <c r="F25">
-        <v>-0.2088290843910547</v>
+        <v>-0.4361148756363775</v>
       </c>
       <c r="G25">
-        <v>0.3500923506551334</v>
+        <v>-1.243120932301282</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.280767625423028</v>
       </c>
       <c r="E26">
-        <v>-26.96762179468752</v>
+        <v>-29.24328413844405</v>
       </c>
       <c r="F26">
-        <v>-0.9010485059686419</v>
+        <v>-0.5302406068816797</v>
       </c>
       <c r="G26">
-        <v>1.256963332409847</v>
+        <v>-1.908706112971755</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.7940822146202219</v>
       </c>
       <c r="E27">
-        <v>-28.20674813740636</v>
+        <v>-28.78065976229446</v>
       </c>
       <c r="F27">
-        <v>-0.3252113910147741</v>
+        <v>-0.0522013758697242</v>
       </c>
       <c r="G27">
-        <v>2.087546102757595</v>
+        <v>-0.9613968174548437</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4538769533990513</v>
       </c>
       <c r="E28">
-        <v>-29.61700777711207</v>
+        <v>-29.2816855980291</v>
       </c>
       <c r="F28">
-        <v>-0.4640565365002076</v>
+        <v>0.1895154038997687</v>
       </c>
       <c r="G28">
-        <v>2.295514573534611</v>
+        <v>-1.466397365651888</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2503216289720437</v>
       </c>
       <c r="E29">
-        <v>-26.68791606912976</v>
+        <v>-28.60465609151234</v>
       </c>
       <c r="F29">
-        <v>-0.4898634945670234</v>
+        <v>-0.09924353230730532</v>
       </c>
       <c r="G29">
-        <v>2.11527523219453</v>
+        <v>-1.72280573875952</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.169989591946184</v>
       </c>
       <c r="E30">
-        <v>-27.19537233795529</v>
+        <v>-28.95947561543534</v>
       </c>
       <c r="F30">
-        <v>0.05985850964618732</v>
+        <v>-0.2028051966378967</v>
       </c>
       <c r="G30">
-        <v>1.344153170277632</v>
+        <v>-1.80756894674702</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1957651671412927</v>
       </c>
       <c r="E31">
-        <v>-25.40064751923537</v>
+        <v>-28.62202731780577</v>
       </c>
       <c r="F31">
-        <v>-0.2055147864124539</v>
+        <v>0.06646639641831897</v>
       </c>
       <c r="G31">
-        <v>0.2590291745064008</v>
+        <v>-1.972288450598997</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.3126457798180481</v>
       </c>
       <c r="E32">
-        <v>-26.10434973765731</v>
+        <v>-28.63185863487642</v>
       </c>
       <c r="F32">
-        <v>-0.02313065023587835</v>
+        <v>0.1401223407730426</v>
       </c>
       <c r="G32">
-        <v>1.204901693259268</v>
+        <v>-2.111940503627613</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5017648931388722</v>
       </c>
       <c r="E33">
-        <v>-25.3954669449706</v>
+        <v>-27.96411250007539</v>
       </c>
       <c r="F33">
-        <v>0.2441528610536185</v>
+        <v>-0.06742262689616511</v>
       </c>
       <c r="G33">
-        <v>1.031515181185479</v>
+        <v>-1.701250776753326</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7445943006771236</v>
       </c>
       <c r="E34">
-        <v>-24.85499810062915</v>
+        <v>-27.61616719969603</v>
       </c>
       <c r="F34">
-        <v>0.2081776931174388</v>
+        <v>0.1031257958292111</v>
       </c>
       <c r="G34">
-        <v>-0.2732370267520813</v>
+        <v>-2.620854116652076</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.024902654016597</v>
       </c>
       <c r="E35">
-        <v>-25.46543639686311</v>
+        <v>-26.57957685697025</v>
       </c>
       <c r="F35">
-        <v>-0.1194780628554888</v>
+        <v>-0.06633498049628936</v>
       </c>
       <c r="G35">
-        <v>-0.499585646363131</v>
+        <v>-3.083492924128607</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.331068981725319</v>
       </c>
       <c r="E36">
-        <v>-23.01305035495725</v>
+        <v>-25.68171631546945</v>
       </c>
       <c r="F36">
-        <v>0.02346584453899664</v>
+        <v>-0.1914168015842091</v>
       </c>
       <c r="G36">
-        <v>-0.06312994355669618</v>
+        <v>-2.422300837388747</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.654063645057217</v>
       </c>
       <c r="E37">
-        <v>-23.08521611674348</v>
+        <v>-25.7149281438417</v>
       </c>
       <c r="F37">
-        <v>0.113728070217642</v>
+        <v>0.3961599362021334</v>
       </c>
       <c r="G37">
-        <v>-0.3309530776837352</v>
+        <v>-2.707047480312541</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.98788677316344</v>
       </c>
       <c r="E38">
-        <v>-21.6217763425287</v>
+        <v>-24.62951632283923</v>
       </c>
       <c r="F38">
-        <v>-0.2247312534225968</v>
+        <v>0.2740130208223323</v>
       </c>
       <c r="G38">
-        <v>-0.2634212592281422</v>
+        <v>-2.980491920765262</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.327726915343258</v>
       </c>
       <c r="E39">
-        <v>-22.73379294832624</v>
+        <v>-24.481788443761</v>
       </c>
       <c r="F39">
-        <v>0.5485753964802285</v>
+        <v>0.2696359274659397</v>
       </c>
       <c r="G39">
-        <v>0.2198157625937336</v>
+        <v>-2.57736679044821</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.668517640536829</v>
       </c>
       <c r="E40">
-        <v>-21.98771779861453</v>
+        <v>-23.92090523859298</v>
       </c>
       <c r="F40">
-        <v>0.2710540924595325</v>
+        <v>0.3320136496315481</v>
       </c>
       <c r="G40">
-        <v>0.202485056695649</v>
+        <v>-2.388619347072202</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.005991645146944</v>
       </c>
       <c r="E41">
-        <v>-19.62856850805259</v>
+        <v>-23.45415089414838</v>
       </c>
       <c r="F41">
-        <v>1.085079142046967</v>
+        <v>0.6850969714008094</v>
       </c>
       <c r="G41">
-        <v>-1.150505110294632</v>
+        <v>-3.237721309166633</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.338785404296832</v>
       </c>
       <c r="E42">
-        <v>-21.10866853814159</v>
+        <v>-22.73725723094211</v>
       </c>
       <c r="F42">
-        <v>0.2886776089540919</v>
+        <v>0.6994078466515736</v>
       </c>
       <c r="G42">
-        <v>-0.8194108298210417</v>
+        <v>-3.158831008965801</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.664866741539896</v>
       </c>
       <c r="E43">
-        <v>-17.40454435340552</v>
+        <v>-21.2680210099975</v>
       </c>
       <c r="F43">
-        <v>0.8562211094711313</v>
+        <v>0.7544379499543504</v>
       </c>
       <c r="G43">
-        <v>-0.3854049307136677</v>
+        <v>-3.047633094847221</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.983199093269205</v>
       </c>
       <c r="E44">
-        <v>-18.31508915060181</v>
+        <v>-21.93659132706793</v>
       </c>
       <c r="F44">
-        <v>1.233454654501609</v>
+        <v>0.2785905790902024</v>
       </c>
       <c r="G44">
-        <v>-1.085962714461001</v>
+        <v>-4.046835191692208</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.293353149527699</v>
       </c>
       <c r="E45">
-        <v>-17.7273566230423</v>
+        <v>-20.52998843012342</v>
       </c>
       <c r="F45">
-        <v>0.8397266577465875</v>
+        <v>1.08486376652224</v>
       </c>
       <c r="G45">
-        <v>-3.184606916534567</v>
+        <v>-3.261587031959239</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.593646689276777</v>
       </c>
       <c r="E46">
-        <v>-16.81846471885882</v>
+        <v>-20.17592516135971</v>
       </c>
       <c r="F46">
-        <v>0.5318349196370532</v>
+        <v>0.6925473078215881</v>
       </c>
       <c r="G46">
-        <v>-1.828941828748555</v>
+        <v>-3.587639351576519</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.88441093712547</v>
       </c>
       <c r="E47">
-        <v>-17.90874464941954</v>
+        <v>-19.54553893712195</v>
       </c>
       <c r="F47">
-        <v>0.4865737531154911</v>
+        <v>1.021896246765838</v>
       </c>
       <c r="G47">
-        <v>-1.396084688943308</v>
+        <v>-3.096569579008728</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.16942799518838</v>
       </c>
       <c r="E48">
-        <v>-14.93949669817421</v>
+        <v>-18.6088014462653</v>
       </c>
       <c r="F48">
-        <v>1.066631399986622</v>
+        <v>1.034000351255544</v>
       </c>
       <c r="G48">
-        <v>-1.001646430121303</v>
+        <v>-4.092858395779156</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.452232850813564</v>
       </c>
       <c r="E49">
-        <v>-15.48654541524881</v>
+        <v>-18.13024589855672</v>
       </c>
       <c r="F49">
-        <v>0.9204096427792593</v>
+        <v>1.184615769167356</v>
       </c>
       <c r="G49">
-        <v>-1.189112692373612</v>
+        <v>-3.814501105746156</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.737778385530314</v>
       </c>
       <c r="E50">
-        <v>-15.26989869024785</v>
+        <v>-17.92102134245433</v>
       </c>
       <c r="F50">
-        <v>0.956128845187974</v>
+        <v>1.002572091993331</v>
       </c>
       <c r="G50">
-        <v>-2.124835078503074</v>
+        <v>-3.851976481250706</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.030589600623238</v>
       </c>
       <c r="E51">
-        <v>-14.58700028141715</v>
+        <v>-16.56779104016423</v>
       </c>
       <c r="F51">
-        <v>1.138129447257053</v>
+        <v>1.160917834508068</v>
       </c>
       <c r="G51">
-        <v>-2.243918712096198</v>
+        <v>-4.254376602094658</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.331651792016018</v>
       </c>
       <c r="E52">
-        <v>-14.24772248028848</v>
+        <v>-16.30623090995519</v>
       </c>
       <c r="F52">
-        <v>1.310221118453845</v>
+        <v>1.095756797869053</v>
       </c>
       <c r="G52">
-        <v>-1.363975707757916</v>
+        <v>-4.421665089285109</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.643845475397819</v>
       </c>
       <c r="E53">
-        <v>-11.74322728797635</v>
+        <v>-16.40236135619002</v>
       </c>
       <c r="F53">
-        <v>1.471557267292688</v>
+        <v>1.073046277153902</v>
       </c>
       <c r="G53">
-        <v>-2.493116717019297</v>
+        <v>-4.256131191230471</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.971528551435789</v>
       </c>
       <c r="E54">
-        <v>-11.72330653081661</v>
+        <v>-14.68380547027912</v>
       </c>
       <c r="F54">
-        <v>1.187281455469565</v>
+        <v>1.581864327384276</v>
       </c>
       <c r="G54">
-        <v>-2.521458297380998</v>
+        <v>-4.743721580436489</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.317533117276805</v>
       </c>
       <c r="E55">
-        <v>-10.43501001732248</v>
+        <v>-14.28118790320516</v>
       </c>
       <c r="F55">
-        <v>0.9741375525248352</v>
+        <v>1.326259968106849</v>
       </c>
       <c r="G55">
-        <v>-1.763849882355405</v>
+        <v>-4.284969353423063</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.685009170437706</v>
       </c>
       <c r="E56">
-        <v>-12.97559714747575</v>
+        <v>-15.33781674341489</v>
       </c>
       <c r="F56">
-        <v>1.416886675442726</v>
+        <v>1.25696703486267</v>
       </c>
       <c r="G56">
-        <v>-1.992641684574436</v>
+        <v>-5.293090059950846</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.074625527519869</v>
       </c>
       <c r="E57">
-        <v>-10.95446674226834</v>
+        <v>-14.1873941495583</v>
       </c>
       <c r="F57">
-        <v>0.8889714431082125</v>
+        <v>1.030887346555824</v>
       </c>
       <c r="G57">
-        <v>-3.153842016838119</v>
+        <v>-4.566107501709051</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.481464636522745</v>
       </c>
       <c r="E58">
-        <v>-11.86058269188513</v>
+        <v>-13.55775965200582</v>
       </c>
       <c r="F58">
-        <v>1.058092588798565</v>
+        <v>1.388899454371742</v>
       </c>
       <c r="G58">
-        <v>-2.459954982352418</v>
+        <v>-4.86222917910578</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.903253232962458</v>
       </c>
       <c r="E59">
-        <v>-10.25308763101234</v>
+        <v>-13.91949415573852</v>
       </c>
       <c r="F59">
-        <v>1.972875279058115</v>
+        <v>1.530109588792168</v>
       </c>
       <c r="G59">
-        <v>-3.277520687639752</v>
+        <v>-4.92918496263754</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.337623851873717</v>
       </c>
       <c r="E60">
-        <v>-8.64900703954134</v>
+        <v>-13.4882611614101</v>
       </c>
       <c r="F60">
-        <v>1.198999540749567</v>
+        <v>1.095551362753159</v>
       </c>
       <c r="G60">
-        <v>-2.949988554166417</v>
+        <v>-5.397127264067983</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.780763892461938</v>
       </c>
       <c r="E61">
-        <v>-9.60870389361688</v>
+        <v>-13.7062347292953</v>
       </c>
       <c r="F61">
-        <v>0.9292218152102405</v>
+        <v>1.469680186757944</v>
       </c>
       <c r="G61">
-        <v>-1.984203103994834</v>
+        <v>-5.551524486928512</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.2284389945017</v>
       </c>
       <c r="E62">
-        <v>-8.601335793662594</v>
+        <v>-12.52556645754148</v>
       </c>
       <c r="F62">
-        <v>1.092259430694434</v>
+        <v>1.331967419512138</v>
       </c>
       <c r="G62">
-        <v>-2.593499078861078</v>
+        <v>-5.771510238013082</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.67288361407204</v>
       </c>
       <c r="E63">
-        <v>-9.030612487219706</v>
+        <v>-13.2234133590715</v>
       </c>
       <c r="F63">
-        <v>1.576218175166794</v>
+        <v>1.655060527830446</v>
       </c>
       <c r="G63">
-        <v>-1.580237095110807</v>
+        <v>-4.809283624296215</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.09972097052759</v>
       </c>
       <c r="E64">
-        <v>-8.614644978771137</v>
+        <v>-12.85382648140949</v>
       </c>
       <c r="F64">
-        <v>1.245865254930351</v>
+        <v>0.8684246180491736</v>
       </c>
       <c r="G64">
-        <v>-3.360674970495165</v>
+        <v>-5.097307707303887</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.49897707305345</v>
       </c>
       <c r="E65">
-        <v>-11.06443620507061</v>
+        <v>-12.70899229722217</v>
       </c>
       <c r="F65">
-        <v>1.795371055251431</v>
+        <v>1.141494275647225</v>
       </c>
       <c r="G65">
-        <v>-2.937189985111595</v>
+        <v>-5.497420241180203</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.85989757988523</v>
       </c>
       <c r="E66">
-        <v>-9.176551619064899</v>
+        <v>-12.49789748135461</v>
       </c>
       <c r="F66">
-        <v>1.23506168726304</v>
+        <v>1.316861311554686</v>
       </c>
       <c r="G66">
-        <v>-3.882201762024252</v>
+        <v>-5.602281771136618</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.17343943870841</v>
       </c>
       <c r="E67">
-        <v>-7.23258188247419</v>
+        <v>-12.94049694544229</v>
       </c>
       <c r="F67">
-        <v>0.3788031540112753</v>
+        <v>1.220330001371654</v>
       </c>
       <c r="G67">
-        <v>-2.805602421016644</v>
+        <v>-5.484466076485035</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.43223168612096</v>
       </c>
       <c r="E68">
-        <v>-8.604786490856439</v>
+        <v>-12.78398382678919</v>
       </c>
       <c r="F68">
-        <v>1.227140838157472</v>
+        <v>1.191366963500172</v>
       </c>
       <c r="G68">
-        <v>-3.122881794954855</v>
+        <v>-5.13013838741684</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.62784206747386</v>
       </c>
       <c r="E69">
-        <v>-9.966471454118869</v>
+        <v>-11.89594101693702</v>
       </c>
       <c r="F69">
-        <v>0.8438983159870858</v>
+        <v>1.110538185804608</v>
       </c>
       <c r="G69">
-        <v>-3.518260248710013</v>
+        <v>-5.671389409268904</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.74899329392144</v>
       </c>
       <c r="E70">
-        <v>-7.53333595521961</v>
+        <v>-13.07915429108315</v>
       </c>
       <c r="F70">
-        <v>1.133575083276462</v>
+        <v>1.321846426584733</v>
       </c>
       <c r="G70">
-        <v>-3.402841389028862</v>
+        <v>-4.918256851812405</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.79195584548119</v>
       </c>
       <c r="E71">
-        <v>-9.088499970459756</v>
+        <v>-12.34355350175119</v>
       </c>
       <c r="F71">
-        <v>0.5207786999118882</v>
+        <v>1.027741207159991</v>
       </c>
       <c r="G71">
-        <v>-2.616815251094165</v>
+        <v>-4.589410431759981</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.752381445261</v>
       </c>
       <c r="E72">
-        <v>-9.051067604312353</v>
+        <v>-12.81506274390383</v>
       </c>
       <c r="F72">
-        <v>0.9875305966932977</v>
+        <v>1.152102348607476</v>
       </c>
       <c r="G72">
-        <v>-2.770222620838453</v>
+        <v>-5.371579784141427</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.63143304807811</v>
       </c>
       <c r="E73">
-        <v>-6.910340200562375</v>
+        <v>-12.60278599632028</v>
       </c>
       <c r="F73">
-        <v>1.22092642590167</v>
+        <v>0.7774002943599527</v>
       </c>
       <c r="G73">
-        <v>-2.825647774256931</v>
+        <v>-5.386364680519812</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.43231083276588</v>
       </c>
       <c r="E74">
-        <v>-6.899471862943967</v>
+        <v>-12.73177957842877</v>
       </c>
       <c r="F74">
-        <v>0.659920400927524</v>
+        <v>0.8504788666349251</v>
       </c>
       <c r="G74">
-        <v>-3.550650626266243</v>
+        <v>-4.957195488445313</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.15790852191395</v>
       </c>
       <c r="E75">
-        <v>-8.652919641083967</v>
+        <v>-12.49550644707857</v>
       </c>
       <c r="F75">
-        <v>0.2641363962787538</v>
+        <v>0.8790343477442296</v>
       </c>
       <c r="G75">
-        <v>-2.463997158455868</v>
+        <v>-4.681268138838139</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.80997692971214</v>
       </c>
       <c r="E76">
-        <v>-10.37708177781636</v>
+        <v>-14.37675229018903</v>
       </c>
       <c r="F76">
-        <v>0.8950450329055385</v>
+        <v>0.9358239034105525</v>
       </c>
       <c r="G76">
-        <v>-2.977449529414672</v>
+        <v>-4.587553215712449</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.39668749198324</v>
       </c>
       <c r="E77">
-        <v>-10.30468959232975</v>
+        <v>-12.53729520522135</v>
       </c>
       <c r="F77">
-        <v>-0.5917601404179877</v>
+        <v>0.7229566751783579</v>
       </c>
       <c r="G77">
-        <v>-1.870317026898366</v>
+        <v>-4.644050985885651</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.92405111813513</v>
       </c>
       <c r="E78">
-        <v>-11.08640383248182</v>
+        <v>-13.53920649399639</v>
       </c>
       <c r="F78">
-        <v>-0.2791748726041915</v>
+        <v>0.534269491433881</v>
       </c>
       <c r="G78">
-        <v>-1.745151921149601</v>
+        <v>-4.410101353716435</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.40583471107008</v>
       </c>
       <c r="E79">
-        <v>-11.96275865092019</v>
+        <v>-14.38354952967454</v>
       </c>
       <c r="F79">
-        <v>0.2690941751845088</v>
+        <v>0.5251234869395717</v>
       </c>
       <c r="G79">
-        <v>-1.005668742951517</v>
+        <v>-4.1819584184231</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.855565922277888</v>
       </c>
       <c r="E80">
-        <v>-11.41332795651756</v>
+        <v>-14.97825137873185</v>
       </c>
       <c r="F80">
-        <v>0.0610637842172606</v>
+        <v>0.5169972027181085</v>
       </c>
       <c r="G80">
-        <v>-2.216719269945546</v>
+        <v>-3.825776823852914</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.28422794149434</v>
       </c>
       <c r="E81">
-        <v>-11.96752260557626</v>
+        <v>-14.67761051783663</v>
       </c>
       <c r="F81">
-        <v>0.006418871756785617</v>
+        <v>0.4434580581671796</v>
       </c>
       <c r="G81">
-        <v>-2.061861881255058</v>
+        <v>-4.319044798658781</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.700001265142017</v>
       </c>
       <c r="E82">
-        <v>-13.84062625242094</v>
+        <v>-15.6530891038289</v>
       </c>
       <c r="F82">
-        <v>0.8369549404168204</v>
+        <v>0.1598142906723925</v>
       </c>
       <c r="G82">
-        <v>-2.247603349281407</v>
+        <v>-3.754322008933284</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.113069029563164</v>
       </c>
       <c r="E83">
-        <v>-12.32536262166238</v>
+        <v>-16.75175123977782</v>
       </c>
       <c r="F83">
-        <v>-0.0714816271698827</v>
+        <v>-0.1112730837307597</v>
       </c>
       <c r="G83">
-        <v>-0.8205827629419438</v>
+        <v>-4.364683979463174</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.528334040711055</v>
       </c>
       <c r="E84">
-        <v>-12.46901487413369</v>
+        <v>-17.6584558910156</v>
       </c>
       <c r="F84">
-        <v>-0.3109353071949274</v>
+        <v>-0.0003198970649883613</v>
       </c>
       <c r="G84">
-        <v>0.2628296807854842</v>
+        <v>-4.575906716505293</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.95718951712727</v>
       </c>
       <c r="E85">
-        <v>-15.07087678608474</v>
+        <v>-18.10409396116243</v>
       </c>
       <c r="F85">
-        <v>0.4377290692094182</v>
+        <v>0.001160395483814355</v>
       </c>
       <c r="G85">
-        <v>-2.22128782278974</v>
+        <v>-3.600908018097918</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.40758500402506</v>
       </c>
       <c r="E86">
-        <v>-15.73794364978463</v>
+        <v>-18.8737669889281</v>
       </c>
       <c r="F86">
-        <v>-0.8186160089812576</v>
+        <v>-0.1933319870194816</v>
       </c>
       <c r="G86">
-        <v>-1.719011853571516</v>
+        <v>-3.82152608338049</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.884500248853239</v>
       </c>
       <c r="E87">
-        <v>-18.06041230088444</v>
+        <v>-20.33098463985635</v>
       </c>
       <c r="F87">
-        <v>0.02092607008201336</v>
+        <v>-0.2490504636339847</v>
       </c>
       <c r="G87">
-        <v>0.02533445434370848</v>
+        <v>-3.381945225584983</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.390712042170117</v>
       </c>
       <c r="E88">
-        <v>-17.14936031459929</v>
+        <v>-20.39878042422518</v>
       </c>
       <c r="F88">
-        <v>-0.6169267704824396</v>
+        <v>-0.5531524208757113</v>
       </c>
       <c r="G88">
-        <v>-0.5012508507693844</v>
+        <v>-3.60757545681401</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.931922149784782</v>
       </c>
       <c r="E89">
-        <v>-19.27264856494573</v>
+        <v>-21.91023107986928</v>
       </c>
       <c r="F89">
-        <v>-1.280777921983755</v>
+        <v>-0.6917159214441929</v>
       </c>
       <c r="G89">
-        <v>0.685394334509137</v>
+        <v>-3.872813054874879</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.511015307300648</v>
       </c>
       <c r="E90">
-        <v>-20.70944732657339</v>
+        <v>-23.35303912650512</v>
       </c>
       <c r="F90">
-        <v>-0.9043835131323128</v>
+        <v>-0.8659853705429446</v>
       </c>
       <c r="G90">
-        <v>-2.121435148234243</v>
+        <v>-3.661656528743544</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.138865017033793</v>
       </c>
       <c r="E91">
-        <v>-21.64141180582596</v>
+        <v>-24.04033921207127</v>
       </c>
       <c r="F91">
-        <v>-1.063834297762384</v>
+        <v>-0.885934942704565</v>
       </c>
       <c r="G91">
-        <v>-0.8853370336900882</v>
+        <v>-3.122292517848865</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.823866122234766</v>
       </c>
       <c r="E92">
-        <v>-23.20725396277619</v>
+        <v>-26.62181393403979</v>
       </c>
       <c r="F92">
-        <v>-0.9277940043028297</v>
+        <v>-0.9685273146006897</v>
       </c>
       <c r="G92">
-        <v>-1.101158118486255</v>
+        <v>-3.734577915337071</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.573123848527017</v>
       </c>
       <c r="E93">
-        <v>-24.30789957034047</v>
+        <v>-27.11394131834936</v>
       </c>
       <c r="F93">
-        <v>-1.160920614105292</v>
+        <v>-1.126542538521709</v>
       </c>
       <c r="G93">
-        <v>-0.679904440796154</v>
+        <v>-3.84441519523901</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.390560297328443</v>
       </c>
       <c r="E94">
-        <v>-25.54635569890618</v>
+        <v>-29.04131419770196</v>
       </c>
       <c r="F94">
-        <v>-1.33057605677045</v>
+        <v>-1.595188083185918</v>
       </c>
       <c r="G94">
-        <v>-1.495126279841684</v>
+        <v>-3.55497750928607</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.282277696459218</v>
       </c>
       <c r="E95">
-        <v>-29.08250519727573</v>
+        <v>-30.68532234449859</v>
       </c>
       <c r="F95">
-        <v>-1.21478520447233</v>
+        <v>-1.737563730542083</v>
       </c>
       <c r="G95">
-        <v>-0.6093269204444315</v>
+        <v>-5.050559493743839</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.252163498827347</v>
       </c>
       <c r="E96">
-        <v>-30.54018248831575</v>
+        <v>-32.38932824342285</v>
       </c>
       <c r="F96">
-        <v>-2.610282752454877</v>
+        <v>-2.033082973123404</v>
       </c>
       <c r="G96">
-        <v>-1.487078343635716</v>
+        <v>-4.343208470549921</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.301173474464809</v>
       </c>
       <c r="E97">
-        <v>-32.09227393394169</v>
+        <v>-34.56682685611511</v>
       </c>
       <c r="F97">
-        <v>-2.22027246860362</v>
+        <v>-1.967825845865665</v>
       </c>
       <c r="G97">
-        <v>-1.131691279994954</v>
+        <v>-4.412749790147852</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.434437869212424</v>
       </c>
       <c r="E98">
-        <v>-34.90752886231919</v>
+        <v>-35.88158097899905</v>
       </c>
       <c r="F98">
-        <v>-2.110063984232965</v>
+        <v>-2.223083119201319</v>
       </c>
       <c r="G98">
-        <v>-1.359499850188822</v>
+        <v>-4.139321902422827</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.636770081311641</v>
       </c>
       <c r="E99">
-        <v>-36.56147474532565</v>
+        <v>-38.49244776151435</v>
       </c>
       <c r="F99">
-        <v>-2.525373436933123</v>
+        <v>-2.310082405680337</v>
       </c>
       <c r="G99">
-        <v>-1.010227364159094</v>
+        <v>-5.312714973907646</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.912891507017533</v>
       </c>
       <c r="E100">
-        <v>-37.97345973362828</v>
+        <v>-40.57862063889392</v>
       </c>
       <c r="F100">
-        <v>-2.500270591158686</v>
+        <v>-2.437945056139454</v>
       </c>
       <c r="G100">
-        <v>-2.168365441798951</v>
+        <v>-4.828329192783642</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.228734069400304</v>
       </c>
       <c r="E101">
-        <v>-40.63360763453205</v>
+        <v>-42.70380179137556</v>
       </c>
       <c r="F101">
-        <v>-2.716694829018502</v>
+        <v>-2.842036757470901</v>
       </c>
       <c r="G101">
-        <v>-1.947191204865782</v>
+        <v>-5.774595666455683</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.611041869426645</v>
       </c>
       <c r="E102">
-        <v>-43.1858736991511</v>
+        <v>-45.11532061959921</v>
       </c>
       <c r="F102">
-        <v>-2.856864533981012</v>
+        <v>-2.975569582802181</v>
       </c>
       <c r="G102">
-        <v>-3.230802268989557</v>
+        <v>-5.79336977020889</v>
       </c>
     </row>
   </sheetData>
